--- a/気分（きぶん）.xlsx
+++ b/気分（きぶん）.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\苗欣奕的东西\折跃\Japanese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C0BCD4-D0F2-4B34-94B1-BA1B4467F76A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790D48BE-618D-473A-86EF-B0763179A676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="恋人の気持ち" sheetId="7" r:id="rId1"/>
@@ -3126,18 +3126,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6A21B02-ECFE-46F5-94D4-AD9AC3F7C427}">
-  <dimension ref="A2:I36"/>
+  <dimension ref="A2:G36"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="18" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -3147,17 +3146,17 @@
       <c r="C2" t="s">
         <v>27</v>
       </c>
-      <c r="G2" t="s">
+      <c r="E2" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="18" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>38</v>
       </c>
@@ -3167,56 +3166,56 @@
       <c r="C3" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="18" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>246</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H4" t="s">
+      <c r="F4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="18" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="18" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="18" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>104</v>
       </c>
@@ -3226,59 +3225,59 @@
       <c r="C7" t="s">
         <v>106</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>167</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="18" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>169</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="18" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>183</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="I10" t="s">
+      <c r="G10" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="18" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>195</v>
       </c>
@@ -3286,7 +3285,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="18" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>248</v>
       </c>
@@ -3294,7 +3293,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="18" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -3302,7 +3301,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="18" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>270</v>
       </c>
@@ -3310,7 +3309,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="18" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>315</v>
       </c>
@@ -3321,7 +3320,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="18" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>317</v>
       </c>
@@ -4604,82 +4603,82 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC56021F-2D9A-4482-AC46-DF45F03E2A29}">
-  <dimension ref="A2:Q21"/>
+  <dimension ref="A2:P21"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" ht="18" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" ht="18" x14ac:dyDescent="0.45">
+      <c r="A2" s="6" t="s">
+        <v>381</v>
+      </c>
       <c r="B2" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>382</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>370</v>
+      </c>
       <c r="F2" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="G2" s="1" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="18" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>75</v>
       </c>
+      <c r="E3" s="1" t="s">
+        <v>404</v>
+      </c>
       <c r="F3" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="G3" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="18" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>304</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>305</v>
       </c>
+      <c r="E4" s="1" t="s">
+        <v>429</v>
+      </c>
       <c r="F4" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="G4" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>306</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>307</v>
       </c>
+      <c r="E5" s="1" t="s">
+        <v>476</v>
+      </c>
       <c r="F5" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="G5" s="1" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="18" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>73</v>
       </c>
@@ -4687,7 +4686,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="18" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>77</v>
       </c>
@@ -4695,7 +4694,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="18" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>129</v>
       </c>
@@ -4703,7 +4702,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="18" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>145</v>
       </c>
@@ -4711,7 +4710,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>230</v>
       </c>
@@ -4722,7 +4721,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="18" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>451</v>
       </c>
@@ -4730,7 +4729,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="18" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>385</v>
       </c>
@@ -4738,7 +4737,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="18" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>456</v>
       </c>
@@ -4746,16 +4745,16 @@
         <v>457</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="18" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>240</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="Q14" s="8"/>
-    </row>
-    <row r="15" spans="1:17" ht="18" x14ac:dyDescent="0.45">
+      <c r="P14" s="8"/>
+    </row>
+    <row r="15" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>244</v>
       </c>
@@ -4763,7 +4762,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="18" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>268</v>
       </c>
